--- a/app/datos_pipeline/paso2_clusterizacion.xlsx
+++ b/app/datos_pipeline/paso2_clusterizacion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C722"/>
+  <dimension ref="A1:C725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Single face E K/K 99,4x100</t>
+          <t>Single face E K/K 79x92</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -451,7 +451,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Single face E K/K 35x42</t>
+          <t>Single face B BG/BG 79x73,5</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -466,7 +466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Single face E K/K 35x45</t>
+          <t>Single face B K/K 100x50</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Single face E K/K 35x55</t>
+          <t>Single face B K/K 102,5x78,5</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Single face E K/K 37,5x81,9</t>
+          <t>Single face E K/K 89,2x55,4</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -511,7 +511,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Single face E K/K 38,1x62,1</t>
+          <t>Aislador Kraft Montecarlo 5 cm</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -526,7 +526,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Single face E K/K 38.3X73.3</t>
+          <t>Single face E K/K 69,1x63,9</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -541,7 +541,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Single face E K/K 39,6X73,3</t>
+          <t>Single face E K/K 69,3X98,5</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Single face E K/K 39x57</t>
+          <t>Single face E K/K 69,5X40,6</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -571,7 +571,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLONDA #12,5 PX0 IMPRESA OBLEAS JL</t>
+          <t>Single face E K/K 69,5X54</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -586,7 +586,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BLONDA 17 SIN PLASTIFICAR</t>
+          <t>Single face E K/K 69,5x107,5</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -601,7 +601,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 3 PX1 Traviesa</t>
+          <t>Single face E K/K 69,5x35,5</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -616,7 +616,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 3 sancho paisa</t>
+          <t>Single face E K/K 69,5x51,5</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 4  Teres</t>
+          <t>Single face E K/K 69,5x56</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -646,7 +646,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Single face E K/K 79,4x57,5</t>
+          <t>Single face E K/K 69,5x72,5</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -661,7 +661,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Single face E K/K 79,5x69,5</t>
+          <t>AISLADOR B/K</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -676,7 +676,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AISLADOR B/K</t>
+          <t>Single face E K/K 87,5x87,5</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -691,7 +691,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,3x50,9</t>
+          <t>Single face E K/K 71x70</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -706,7 +706,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,2x55,4</t>
+          <t>Single face E K/K 73x66</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -721,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bandeja arepitas con queso</t>
+          <t>Single face E K/K 77X70,5</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -736,7 +736,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bandeja de anchetas las caseritas</t>
+          <t>Bandeja arepitas con queso</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -751,7 +751,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x70</t>
+          <t>Bandeja de anchetas las caseritas</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -766,7 +766,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x75</t>
+          <t>Single face E K/K 89,3x47,3</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -781,7 +781,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,3x47,3</t>
+          <t>BLONDA #12,5 PX0 IMPRESA OBLEAS JL</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -796,7 +796,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Single face E B/B 34,3x47,3</t>
+          <t>Single face B K/K 104,5x77,5</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -811,7 +811,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Single face E B/B 40,3x47,3</t>
+          <t>Single face B K/K 107,5x69,5</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -826,7 +826,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Single face E B/B 40,3x62,3</t>
+          <t>Aislador autopan</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -841,7 +841,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Single face E B/B 41x45</t>
+          <t>BLONDA 17 SIN PLASTIFICAR</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -856,7 +856,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Single face E B/B 49,5x60,5</t>
+          <t>Bandeja Fruver # 3 PX1 Traviesa</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -871,7 +871,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Single face E B/B 57,5x70,3</t>
+          <t>Bandeja Fruver # 3 sancho paisa</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -886,7 +886,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Single face E B/B 59,5x94,5</t>
+          <t>Bandeja Fruver # 4  Teres</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -901,7 +901,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aislador autopan</t>
+          <t>Single face E K/K 99,4x100</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -916,7 +916,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5X40,6</t>
+          <t>Single face E K/K 69,5x93</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -931,7 +931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5X54</t>
+          <t>Single face E K/K 69.3X66.3</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -946,7 +946,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x107,5</t>
+          <t>Single face E K/K 69.5x99.5</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -961,7 +961,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x35,5</t>
+          <t>Single face E K/K 69x98</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -976,7 +976,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x51,5</t>
+          <t>Bandeja plana #25 granel</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -991,7 +991,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x56</t>
+          <t>Single face E K/K 63x52</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1006,7 +1006,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x72,5</t>
+          <t>Single face E K/K 63x53,5</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1021,7 +1021,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x73,5</t>
+          <t>Single face E K/K 64,5x70</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1036,7 +1036,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,5x93</t>
+          <t>Single face E K/K 64,7x67,1</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1051,7 +1051,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Single face E K/K 69.3X66.3</t>
+          <t>Single face E K/K 64x70</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1066,7 +1066,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Single face E K/K 69.5x99.5</t>
+          <t>Single face E K/K 65,5x92</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1081,7 +1081,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bandeja plana #25 granel</t>
+          <t>Single face E K/K 65x90</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1096,7 +1096,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bandeja plana #4 sin plastific</t>
+          <t>Single face E K/K 66,7X51</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1111,7 +1111,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Blonda # 21 Sibiu</t>
+          <t>Single face E K/K 66X72</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1126,7 +1126,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Blonda # 25 Sibiu</t>
+          <t>Single face E K/K 67x67</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1141,7 +1141,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Single face B K/K 73x66</t>
+          <t>Single face E K/K 68X97,5</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1156,7 +1156,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Single face B K/K 74,3X59,6</t>
+          <t>Single face B K/K 53x87</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1171,7 +1171,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Single face B K/K 74X59,5</t>
+          <t>Single face B K/K 54,5X116</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1186,7 +1186,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Single face B K/K 77x113</t>
+          <t>Single face B K/K 54,5X90</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1201,7 +1201,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Single face B K/K 78x59,5</t>
+          <t>Single face B K/K 62x108</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1216,7 +1216,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Single face B K/K 82x42</t>
+          <t>Single face B K/K 62x66</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1231,7 +1231,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Single face B K/K 86X46,2</t>
+          <t>Single Face B/B - NO USAR</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1246,7 +1246,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Single face B K/K 89,5x114,5</t>
+          <t>Single Face BG/BG - NO USAR</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1261,7 +1261,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Single face B K/K 90x57</t>
+          <t>Single Face E K/K 57,1x59,5</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1276,7 +1276,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Single face B K/K 92,3X56,3</t>
+          <t>Single Face E K/K 67,5x72,5</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1291,7 +1291,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Single face B K/K 92X69,5</t>
+          <t>Single face F K/K 67,7X95,3</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1306,7 +1306,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Single face B K/K 93x47</t>
+          <t>Single Face E K/K 67x75</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1321,7 +1321,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Blonda # 25,8</t>
+          <t>Bandeja plana #4 sin plastific</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1336,7 +1336,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Blonda # 30 Sibiu</t>
+          <t>Blonda # 21 Sibiu</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1351,7 +1351,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Blonda #21 Sancho paisa</t>
+          <t>Blonda # 25 Sibiu</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1366,7 +1366,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Blonda 15x20 1X0 PX2</t>
+          <t>Blonda # 25,8</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1381,7 +1381,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Blonda 17B PX0 Obleas JL</t>
+          <t>Blonda # 30 Sibiu</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1396,7 +1396,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Blonda 48cmx 35cm Sibiu</t>
+          <t>Blonda #21 Sancho paisa</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1411,7 +1411,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BANDEJA ONDAS #4</t>
+          <t>Blonda 15x20 1X0 PX2</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1426,7 +1426,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bolsa blanca grande con manigueta</t>
+          <t>Blonda 17B PX0 Obleas JL</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1441,7 +1441,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Single face E K/K 63x52</t>
+          <t>Blonda 48cmx 35cm Sibiu</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1456,7 +1456,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Single face E K/K 63x53,5</t>
+          <t>Single face E K/K 79,4x57,5</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1471,7 +1471,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Single face E K/K 64,5x70</t>
+          <t>Bolsa blanca grande con manigueta</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1486,7 +1486,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Single face E K/K 64,7x67,1</t>
+          <t>Single face E K/K 60X49</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1501,7 +1501,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Single face E K/K 64x70</t>
+          <t>Single face E K/K 60x100</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1516,7 +1516,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Single face E K/K 65,5x92</t>
+          <t>Single face E K/K 60x90</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1531,7 +1531,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Single face E K/K 65x90</t>
+          <t>Single face E K/K 61,9x102,2</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1546,7 +1546,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Single face E K/K 66,7X51</t>
+          <t>Single face E K/K 62,5X72,2</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1561,7 +1561,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Single face E K/K 66X72</t>
+          <t>Single face E K/K 63,1x69,4</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1576,7 +1576,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Single face E K/K 67x67</t>
+          <t>Single face E K/K 63,3x80,3</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1591,7 +1591,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Single face B K/K 64,5x72</t>
+          <t>Single face E K/K 63,5x63,5</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1606,7 +1606,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Single face B K/K 64,5x78,5</t>
+          <t>Single face E K/K 63,5x95</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1621,7 +1621,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Single face B K/K 68x116</t>
+          <t>Bolsa kraft mediana C/M TAG</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1636,7 +1636,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Single face B K/K 69,5X80,5</t>
+          <t>CAJA ARUM FRESH VERDE EXPO</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1651,7 +1651,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Single face B K/K 69,7X59,5</t>
+          <t>Single face B K/K 64,5x72</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1666,7 +1666,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Single face B K/K 70x50</t>
+          <t>Single face B K/K 64,5x78,5</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1681,7 +1681,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Single face B K/K 70x85</t>
+          <t>Single face B K/K 68x116</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1696,7 +1696,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Single face B K/K 71x77,1</t>
+          <t>Single face B K/K 69,5X80,5</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1711,7 +1711,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bolsa kraft mediana C/M TAG</t>
+          <t>Single face B K/K 69,7X59,5</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1726,7 +1726,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAJA ARUM FRESH VERDE EXPO</t>
+          <t>Single face B K/K 70x50</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1741,7 +1741,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAJA ARUM VITAL AZUL EXPO</t>
+          <t>Single face B BG/BG 74.2x59.7</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1756,7 +1756,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAJA ARUM VITAL AZUL NAL</t>
+          <t>Single face B K/K 44x87</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1816,7 +1816,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Single face E K/K 59x94</t>
+          <t>CONTENEDOR 750GR TP Chimba de pollo</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1831,7 +1831,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Single face E K/K 60X49</t>
+          <t>Single face E K/K 56,6X70,7</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1846,7 +1846,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Single face E K/K 60x100</t>
+          <t>Single face E K/K 56x37,5</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1861,7 +1861,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Single face E B/B 70x70</t>
+          <t>Single face E K/K 57,5x74</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1876,7 +1876,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Single face E B/B 70x93</t>
+          <t>Single face E K/K 57,5x74,5</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1891,7 +1891,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Single face E B/B 71,3x101,3</t>
+          <t>Single face E K/K 57X62,5</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1906,7 +1906,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Single face E B/B 71,3x85,7</t>
+          <t>Single face E K/K 59,3x61,5</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1921,7 +1921,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Single face E B/K 102,5x69,6</t>
+          <t>Single face B BG/BG 64x79.5</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1936,7 +1936,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Single face E B/K 42,5x62,2</t>
+          <t>Single face E K/K 59,5x76</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1951,7 +1951,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Single face E B/K 47,5X53,3</t>
+          <t>Single face E K/K 59x47</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1966,7 +1966,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Single face E B/K 48,3x64,3</t>
+          <t>Single face E K/K 59x54</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1981,7 +1981,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Single face E B/K 49,1x65,6</t>
+          <t>Single face E K/K 59x94</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1996,7 +1996,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Single face B K/K 62x66</t>
+          <t>CONTENEDOR C1 TAPA PLANA  AMELIE</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2011,7 +2011,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Single face B K/K 63x63</t>
+          <t>CONTENEDOR C1 TP RAZORBACK</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2026,7 +2026,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Single face E K/K 60x90</t>
+          <t>Single face E K/K 69,5x73,5</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2041,7 +2041,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Single face E K/K 61,9x102,2</t>
+          <t>Single face E K/K 51,5x44,3</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2056,7 +2056,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Single face E K/K 62,5X72,2</t>
+          <t>Single face E K/K 51,5x77</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2071,7 +2071,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Single face E K/K 63,1x69,4</t>
+          <t>Single face E K/K 51X61</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2086,7 +2086,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Single face E K/K 63,3x80,3</t>
+          <t>Single face E K/K 52,5X63,5</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2101,7 +2101,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Single face E K/K 63,5x63,5</t>
+          <t>Single face E K/K 53X79</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2116,7 +2116,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Single face E K/K 63,5x95</t>
+          <t>Single face E K/K 54,1x72,4</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2131,7 +2131,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CONTENEDOR 750GR TP Chimba de pollo</t>
+          <t>RECIPIENTE ONDAS 500GR</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2146,7 +2146,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TAPA PLANA  AMELIE</t>
+          <t>Single face E K/K 79,5x69,5</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2161,7 +2161,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TP RAZORBACK</t>
+          <t>Recipiente Industrial 350gr Px1-Carnivor</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2176,7 +2176,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BANDEJA ONDAS #8</t>
+          <t>Single face B K/K 70x85</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2191,7 +2191,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Caja BG/K 20x20x10 - Maxi pastel</t>
+          <t>Single face B K/K 71x77,1</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2206,7 +2206,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Caja Pizza Bonhomia</t>
+          <t>Single face B K/K 73x66</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2221,7 +2221,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Caja Pizza Dekarla</t>
+          <t>Single face B K/K 74,3X59,6</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2236,7 +2236,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Single face E K/K 56,5X100,5</t>
+          <t>Single face B K/K 74X59,5</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2251,7 +2251,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Single face E K/K 56,6X70,7</t>
+          <t>Single face B K/K 77x113</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2266,7 +2266,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Single face E K/K 56x37,5</t>
+          <t>Single face B K/K 78x59,5</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2281,7 +2281,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Single face E K/K 57,5x74</t>
+          <t>Single face B K/K 82x42</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2296,7 +2296,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Single face E K/K 57,5x74,5</t>
+          <t>Single face B K/K 86X46,2</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2311,7 +2311,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Single face E K/K 57X62,5</t>
+          <t>Single face B K/K 89,5x114,5</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2326,7 +2326,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Single face E K/K 59,3x61,5</t>
+          <t>Single face B K/K 63x63</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2341,7 +2341,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Single face E K/K 97,3X51,5</t>
+          <t>Single face E K/K 54x69</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2356,7 +2356,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Single face B K/K 113,5x71,5</t>
+          <t>Single face E K/K 55X100,5</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2371,7 +2371,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Single face B K/K 116x80</t>
+          <t>Single face E K/K 56,5X100,5</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2386,7 +2386,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Single face B K/K 44,5x63</t>
+          <t>Caja BG/K 20x20x10 - Maxi pastel</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2401,7 +2401,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Single face B K/K 44x87</t>
+          <t>Caja Pizza Bonhomia</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2416,7 +2416,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Single face B K/K 53x87</t>
+          <t>Caja Pizza Dekarla</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2431,7 +2431,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Single face B K/K 54,5X116</t>
+          <t>Caja Pizza Maximo Kraft 31x31x4,5</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2446,7 +2446,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Single face B K/K 54,5X90</t>
+          <t>Single face E K/K 48X61</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2461,7 +2461,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Single face B K/K 62x108</t>
+          <t>Single face E K/K 49.5X88.5</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2476,7 +2476,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Single face E B/B 60x90</t>
+          <t>Single face E K/K 49X90</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2491,7 +2491,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Single face E K/K 59,5x76</t>
+          <t>Single face E K/K 49x69,5</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2506,7 +2506,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Single face E K/K 59x47</t>
+          <t>Single face E K/K 50x51</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2521,7 +2521,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Single face E K/K 59x54</t>
+          <t>Single face E K/K 51,3x45,3</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2536,7 +2536,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Caja Pizza Maximo Kraft 31x31x4,5</t>
+          <t>Caja delivery beige 36 onz</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -2551,7 +2551,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Single Face E K/K 68x73,5</t>
+          <t>Caja delivery beige 64 onz</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2566,7 +2566,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Single Face E K/K 68x90</t>
+          <t>Single face E K/K 44,5x72,8</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2581,7 +2581,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Single face B B/K 59,2x44,5</t>
+          <t>Single face E K/K 44,5x79,5</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -2596,7 +2596,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 49.5x88</t>
+          <t>Single face E K/K 44x49</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -2611,7 +2611,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 55X90.5</t>
+          <t>Single face E K/K 79x73,5</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2626,7 +2626,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 64x79.5</t>
+          <t>Single face E K/K 44x75</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2641,7 +2641,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 74.2x59.7</t>
+          <t>Single face E K/K 45,9X63,5</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -2656,7 +2656,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 79x73,5</t>
+          <t>Single face E K/K 41x99,5</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -2671,7 +2671,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Single face B K/K 100x50</t>
+          <t>Single face E K/K 45X82</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -2686,7 +2686,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Single face B K/K 102,5x78,5</t>
+          <t>Single face E K/K 46,5x70,4</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -2701,7 +2701,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Single face B K/K 104,5x77,5</t>
+          <t>Single face E K/K 47,3X67,3</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -2716,7 +2716,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Single face B K/K 107,5x69,5</t>
+          <t>Caja micro sandupa 28x28x15</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -2731,7 +2731,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Caja delivery beige 36 onz</t>
+          <t>Caja pergamino</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -2746,7 +2746,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Caja delivery beige 64 onz</t>
+          <t>Caja pizza la tavola</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2761,7 +2761,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Caja micro sandupa 28x28x15</t>
+          <t>Caja pizza la tavola invecchia</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2776,7 +2776,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Caja pergamino</t>
+          <t>Single face B K/K 94,5x79,5</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2791,7 +2791,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Caja pizza 27x27x4.5 cm makro</t>
+          <t>Single face B K/K 95,5X116,5</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2806,7 +2806,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Caja pizza la tavola</t>
+          <t>Single face B K/K 96,5X116</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2821,7 +2821,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Caja pizza la tavola invecchia</t>
+          <t>Single face B K/K 96x116</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -2836,7 +2836,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Caja pizza la tavola pasta y vino</t>
+          <t>Single face B K/K 98,5x81,5</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2851,7 +2851,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Single face E K/K 51,3x45,3</t>
+          <t>Single face B K/K 99,4x100</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2866,7 +2866,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Single face E K/K 51,5x44,3</t>
+          <t>Single face C K/K 111,5x83,5</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -2881,7 +2881,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Single face E K/K 51,5x77</t>
+          <t>Porta salseros x 2 und 0.75 onz</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2896,7 +2896,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Single face E K/K 51X61</t>
+          <t>RECIPIENTE FRUVER GRANDE</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2911,7 +2911,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Single face E K/K 52,5X63,5</t>
+          <t>RECIPIENTE INDUSTRIAL 500 GR NAVIDAD</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2926,7 +2926,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Single face E K/K 53X79</t>
+          <t>RECIPIENTE INDUSTRIAL 750 GR</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2941,7 +2941,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Single face E K/K 54,1x72,4</t>
+          <t>RECIPIENTE ONDAS 350GR PX0</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2956,7 +2956,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Single face E K/K 54x69</t>
+          <t>Caja pizza la tavola pasta y vino</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2971,7 +2971,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Single face E K/K 55X100,5</t>
+          <t>Caja wok beige 48onz</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -2986,7 +2986,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Caja wok beige 48onz</t>
+          <t>Contenedor 500gr TP Arandanos - Siecha</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3001,7 +3001,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Single face E B/K 66,9x46,5</t>
+          <t>Single face E K/K 40x55</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3016,7 +3016,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Single face E B/K 67,9x98,2</t>
+          <t>Single face E K/K 40x56</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3031,7 +3031,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Single face E B/K 68,3x41,5</t>
+          <t>Single face E K/K 40x60</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3046,7 +3046,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Single face E B/K 70X41</t>
+          <t>Single face E K/K 40x80</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3061,7 +3061,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Single face E B/K 83,1x51,3</t>
+          <t>Single face E K/K 41x46</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3076,7 +3076,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Single face E B/K 89,4X50,3</t>
+          <t>Single face E K/K 41x72</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3091,7 +3091,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Single Face B/B - NO USAR</t>
+          <t>Single face E K/K 41x78</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3106,7 +3106,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Single Face BG/BG - NO USAR</t>
+          <t>Single face E K/K 43,5x51,5</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3121,7 +3121,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Single Face E K/K 57,1x59,5</t>
+          <t>Single face E K/K 43,5x71,5</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3136,7 +3136,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Single Face E K/K 67,5x72,5</t>
+          <t>Single face E K/K 43,5x75,5</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3151,7 +3151,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Single Face E K/K 67x75</t>
+          <t>Single face E K/K 43,5x95,8</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3166,7 +3166,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Contenedor 500gr TP Arandanos - Siecha</t>
+          <t>Single face E K/K 43.5x63.5</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3196,7 +3196,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Contenedor P1 TA Belga</t>
+          <t>Single face E K/K 35x45</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3211,7 +3211,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Single face E K/K 48X61</t>
+          <t>Single face E K/K 35x55</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3226,7 +3226,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Single face E K/K 49.5X88.5</t>
+          <t>Single face E K/K 37,5x81,9</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3241,7 +3241,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Single face E K/K 49X90</t>
+          <t>Single face E K/K 38,1x62,1</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3256,7 +3256,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Single face E K/K 49x69,5</t>
+          <t>Single face E K/K 38.3X73.3</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3271,7 +3271,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Single face E K/K 50x51</t>
+          <t>Single face E K/K 39,6X73,3</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3286,7 +3286,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP chimba de pollo</t>
+          <t>Single face E K/K 39x57</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3301,7 +3301,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Contenedor P1 Tapa Plana il Forno</t>
+          <t>Single face E K/K 40,2X91,4</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3316,7 +3316,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Single face E K/K 43.5x63.5</t>
+          <t>Single face E K/K 40,8X72,6</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -3331,7 +3331,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Single face E B/K 50,3x89,1</t>
+          <t>Single face E K/K 40,9X63,4</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -3346,7 +3346,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Single face E B/K 51,5x35,5</t>
+          <t>Single face E K/K 40X62,8</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3361,7 +3361,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Single face E B/K 56X62</t>
+          <t>Single face E K/K 40x35</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3376,7 +3376,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Single face E B/K 60X60</t>
+          <t>Single face E K/K 40x52</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3391,7 +3391,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Single face E B/K 64,3x54,4</t>
+          <t>Contenedor P1 TP chimba de pollo</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3406,7 +3406,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 47,5x107,5</t>
+          <t>Single face E BG/BG 44,5x67</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3421,7 +3421,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 48.5x52.5</t>
+          <t>Single face E BG/BG 47,5x107,5</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3436,7 +3436,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 57,5x89,5</t>
+          <t>Single face E BG/BG 48.5x52.5</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3451,7 +3451,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 61X56,5</t>
+          <t>Single face E BG/BG 57,5x89,5</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -3466,7 +3466,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 77x113</t>
+          <t>Single face E BG/BG 61X56,5</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3481,7 +3481,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Single face E K/K 35,3x65,3</t>
+          <t>Single face E BG/BG 77x113</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3496,7 +3496,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Single face E K/K 35x40</t>
+          <t>Single face E K/K 35,3x65,3</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -3511,7 +3511,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Recipiente Industrial 350gr Px1-Carnivor</t>
+          <t>Single face E K/K 35x40</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -3526,7 +3526,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Single face E K/K 44,5x72,8</t>
+          <t>Single face E K/K 35x42</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3541,7 +3541,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Single face E K/K 44,5x79,5</t>
+          <t>Lamina microcorrugada E B/B/B 43x70</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3556,7 +3556,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Single face E K/K 44x49</t>
+          <t>Single face E B/K 51,5x35,5</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3571,7 +3571,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Single face E K/K 44x75</t>
+          <t>Single face C K/K 69,5X87</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3586,7 +3586,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Single face E K/K 45,9X63,5</t>
+          <t>Single face E B/B 34,3x47,3</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3601,7 +3601,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Single face E K/K 45X82</t>
+          <t>Single face E B/B 40,3x47,3</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -3616,7 +3616,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Single face E K/K 46,5x70,4</t>
+          <t>Single face E B/B 40,3x62,3</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -3631,7 +3631,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Single face E K/K 47,3X67,3</t>
+          <t>Single face E B/B 41x45</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3646,7 +3646,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E B/B/B 43x70</t>
+          <t>Single face E B/B 49,5x60,5</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -3661,7 +3661,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E B/B/B 70x43</t>
+          <t>Single face E B/B 57,5x70,3</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -3676,7 +3676,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 100x70</t>
+          <t>Single face E B/B 59,5x94,5</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -3691,7 +3691,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 114x100</t>
+          <t>Single face E B/B 60x90</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -3706,7 +3706,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 25x31</t>
+          <t>Single face B K/K 90x57</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -3721,7 +3721,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Single face E K/K 40,2X91,4</t>
+          <t>Single face B K/K 92,3X56,3</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -3736,7 +3736,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Single face E K/K 40,8X72,6</t>
+          <t>Single face B K/K 92X69,5</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3751,7 +3751,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Single face E K/K 40,9X63,4</t>
+          <t>Single face B K/K 93x47</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -3766,7 +3766,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Single face E K/K 40X62,8</t>
+          <t>Single face E B/K 56X62</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -3781,7 +3781,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x35</t>
+          <t>Single face E B/K 60X60</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -3796,7 +3796,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Porta salseros x 2 und 0.75 onz</t>
+          <t>Single face E B/K 64,3x54,4</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -3811,7 +3811,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RECIPIENTE FRUVER GRANDE</t>
+          <t>Single face E B/K 66,9x46,5</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -3826,7 +3826,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RECIPIENTE INDUSTRIAL 500 GR NAVIDAD</t>
+          <t>Single face E B/K 67,9x98,2</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -3841,7 +3841,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RECIPIENTE INDUSTRIAL 750 GR</t>
+          <t>Single face E B/K 68,3x41,5</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -3856,7 +3856,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RECIPIENTE ONDAS 350GR PX0</t>
+          <t>Single face E B/K 70X41</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -3871,7 +3871,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RECIPIENTE ONDAS 500GR</t>
+          <t>Single face E B/K 83,1x51,3</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -3886,7 +3886,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 41x53.5</t>
+          <t>Single face E B/K 89,4X50,3</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -3901,7 +3901,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 44,5x67</t>
+          <t>Single face E BG/BG 41x53.5</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -3916,7 +3916,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 50x95</t>
+          <t>Lamina microcorrugada E B/B/B 70x43</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -3931,7 +3931,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 64x78</t>
+          <t>Lamina microcorrugada E K/K/K 100x70</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -3946,7 +3946,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 66,5x60,5</t>
+          <t>Lamina microcorrugada E K/K/K 114x100</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -3961,7 +3961,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 68,5x62</t>
+          <t>Lamina microcorrugada E K/K/K 25x31</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -3976,7 +3976,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 69x49</t>
+          <t>Lamina microcorrugada E K/K/K 50x95</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -3991,7 +3991,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 75x72</t>
+          <t>Lamina microcorrugada E K/K/K 64x78</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4006,7 +4006,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x52</t>
+          <t>Lamina microcorrugada E K/K/K 66,5x60,5</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4021,7 +4021,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x55</t>
+          <t>Lamina microcorrugada E K/K/K 68,5x62</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4036,7 +4036,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x56</t>
+          <t>Lamina microcorrugada E K/K/K 69x49</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -4051,7 +4051,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x60</t>
+          <t>Lamina microcorrugada E K/K/K 75x72</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4066,7 +4066,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x80</t>
+          <t>Single face E B/B 70x70</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4081,7 +4081,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Single face E K/K 41x46</t>
+          <t>Single face E B/B 70x93</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -4096,7 +4096,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Single face E K/K 41x72</t>
+          <t>Single face E B/B 71,3x101,3</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4111,7 +4111,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Single face E K/K 41x78</t>
+          <t>Single face E B/B 71,3x85,7</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -4126,7 +4126,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Single face E K/K 41x99,5</t>
+          <t>Single face E B/K 102,5x69,6</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4141,7 +4141,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Single face E K/K 43,5x51,5</t>
+          <t>Single face E B/K 42,5x62,2</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4156,7 +4156,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Single face E K/K 43,5x71,5</t>
+          <t>Single face E B/K 47,5X53,3</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4171,7 +4171,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Single face E K/K 43,5x75,5</t>
+          <t>Single face E B/K 48,3x64,3</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4186,7 +4186,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Single face E K/K 43,5x95,8</t>
+          <t>Single face E B/K 49,1x65,6</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4201,7 +4201,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PLATO CUADRADO 15X15</t>
+          <t>Single face E B/K 50,3x89,1</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4216,7 +4216,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PORTA SANDUPA DELIVERY</t>
+          <t>PLATO CUADRADO 15X15</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -4231,7 +4231,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Papel antigraso sin impresion 43x63</t>
+          <t>PORTA SANDUPA DELIVERY</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4246,7 +4246,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Parrillas Caja doble Pizza</t>
+          <t>Papel antigraso sin impresion 43x63</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -4261,7 +4261,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Single face B K/K 94,5x79,5</t>
+          <t>Plato cuadrado 10x10(D)</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -4276,7 +4276,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Single face B K/K 95,5X116,5</t>
+          <t>Single face E K/K 70x70</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4291,7 +4291,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Single face B K/K 96,5X116</t>
+          <t>Single face E K/K 70x75</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -4306,7 +4306,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Single face B K/K 96x116</t>
+          <t>Single face E K/K 97,3X51,5</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4321,7 +4321,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Single face B K/K 98,5x81,5</t>
+          <t>Single face E K/K 89,3x50,9</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -4336,7 +4336,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Single face B K/K 99,4x100</t>
+          <t>Single face B K/K 113,5x71,5</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -4351,7 +4351,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Single face C K/K 111,5x83,5</t>
+          <t>Single face B K/K 116x80</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -4366,7 +4366,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Single face C K/K 69,5X87</t>
+          <t>Single face B K/K 44,5x63</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4381,7 +4381,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Single face E K/K 71x70</t>
+          <t>BANDEJA ONDAS #4</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -4396,7 +4396,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Single face E K/K 73x66</t>
+          <t>BANDEJA ONDAS #8</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -4411,7 +4411,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Single face E K/K 77X70,5</t>
+          <t>Bandeja fruver # 3 Country fruit</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -4426,7 +4426,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Bandeja fruver # 3 Country fruit</t>
+          <t>Single Face E K/K 68x73,5</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -4441,7 +4441,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Single face E K/K 68X97,5</t>
+          <t>Single Face E K/K 68x90</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -4456,7 +4456,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,1x63,9</t>
+          <t>Single face B B/K 59,2x44,5</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -4471,7 +4471,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Single face F K/K 67,7X95,3</t>
+          <t>Single face B BG/BG 49.5x88</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -4486,7 +4486,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Plato cuadrado 10x10(D)</t>
+          <t>Single face B BG/BG 55X90.5</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -4501,7 +4501,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Single face E K/K 69,3X98,5</t>
+          <t>Single face E K/K 81,4X48</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -4516,11 +4516,11 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Single face E K/K 79x73,5</t>
+          <t>BANDEJA ONDAS #7</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -4531,11 +4531,11 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Single face E K/K 79x92</t>
+          <t>Contenedor tapa plana chicharrón sin imp</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -4546,11 +4546,11 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Single face E K/K 81,4X48</t>
+          <t>Single Face E K/K 67,5x90</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -4561,11 +4561,11 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Single face E K/K 87,5x87,5</t>
+          <t>Bolsa blanca boutique con manigueta25,5+13x33</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -4576,11 +4576,11 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Contenedor tapa plana chicharrón sin imp</t>
+          <t>Single Face B K/K 49,4x79</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4591,11 +4591,11 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>BANDEJA ONDAS #7</t>
+          <t>Single face E K/K 59,5x71,5</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,5x49,5</t>
+          <t>CONTENEDOR P1 TAPA PLANA  AMELIE</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -4621,7 +4621,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Bolsa blanca boutique con manigueta25,5+13x33</t>
+          <t>Recipiente 250g Px2 Granel</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -4636,7 +4636,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TAPA PLANA  AMELIE</t>
+          <t>Single face E K/K 44x63</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -4651,7 +4651,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Single face E K/K 59,5x71,5</t>
+          <t>Caja regalo beige mediana PX1</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -4666,7 +4666,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E B/B/B 90x50</t>
+          <t>Caja regalo las caseritas</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -4681,7 +4681,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Contenedor 1000 gr TP sancho paisa</t>
+          <t>Caja pizza 27x27x4.5 cm makro</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -4696,7 +4696,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Caja regalo beige mediana PX1</t>
+          <t>Contenedor 1000 gr TP sancho paisa</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -4711,7 +4711,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Caja regalo las caseritas</t>
+          <t>Contenedor P1 TA Belga</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -4726,7 +4726,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Single face E K/K 44x63</t>
+          <t>Single face E K/K 46,7x50,2</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -4741,7 +4741,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Contenedor P3 TP AGCINCO</t>
+          <t>Single face E K/K 45.3x77.3</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -4756,7 +4756,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Contenedor chuzo sancho paisa</t>
+          <t>Single face E K/K 89,5x49,5</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -4771,7 +4771,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Single face E K/K 45.3x77.3</t>
+          <t>Lamina microcorrugada E B/B/B 90x50</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -4786,7 +4786,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Single Face B K/K 49,4x79</t>
+          <t>Contenedor P3 TP AGCINCO</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -4801,7 +4801,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Single face E K/K 46,7x50,2</t>
+          <t>Contenedor chuzo sancho paisa</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -4816,11 +4816,11 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Single Face E K/K 67,5x90</t>
+          <t>Caja wok kraft 26onz</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -4831,11 +4831,11 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Caja pizza  36x36x5 cm makro</t>
+          <t>Caja pizza legrand</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -4846,11 +4846,11 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Recipiente 250g Px2 Granel</t>
+          <t>Single face E K/K 70x90</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -4861,11 +4861,11 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Single face C K/K 87,5x91,5</t>
+          <t>Single face E K/K 43,5x67</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -4876,11 +4876,11 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x90</t>
+          <t>Bandeja formada #1 Legrand</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -4891,11 +4891,11 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Single face E K/K 43,5x67</t>
+          <t>Single face E K/K 85,5x42</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -4906,11 +4906,11 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Caja pizza legrand</t>
+          <t>Bandeja empanadas sancho paisa</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -4921,11 +4921,11 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Caja wok kraft 26onz</t>
+          <t>Single face E K/K 77x113</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Parrilla brosty entero</t>
+          <t>Single face E K/K 76,3x57,3</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -4951,7 +4951,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Parrilla brosty medio</t>
+          <t>Single face E K/K 71x43,5</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -4966,7 +4966,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Single face E K/K 85,5x42</t>
+          <t>Single face C K/K 59,5x99,5</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -4981,7 +4981,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 45x69</t>
+          <t>Parrilla brosty medio</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -4996,7 +4996,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MINICAPACILLO PONQUE ARTESANO 1P 300G BIMBO</t>
+          <t>Parrilla brosty entero</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -5011,7 +5011,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 73x66,5</t>
+          <t>Papel antigraso Starbucks</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -5026,7 +5026,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Single face E K/K 40x40</t>
+          <t>Single face E B/B 69,5x49,5</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -5041,7 +5041,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>RECIPIENTE INDUSTRIAL 500GR PX1 NAVIDAD</t>
+          <t>MINICAPACILLO PONQUE ARTESANO 1P 300G BIMBO</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -5056,7 +5056,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 62x86</t>
+          <t>Lamina microcorrugada E K/K/K 73x66,5</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -5071,7 +5071,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 54x83,5</t>
+          <t>Lamina microcorrugada E K/K/K 70x62</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -5086,7 +5086,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 52x81,5</t>
+          <t>Lamina microcorrugada E K/K/K 62x86</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -5101,7 +5101,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Papel antigraso Starbucks</t>
+          <t>Lamina microcorrugada E K/K/K 54x83,5</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -5116,7 +5116,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 70x62</t>
+          <t>Lamina microcorrugada E K/K/K 52x81,5</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -5131,7 +5131,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Estibas malas y retales de madera</t>
+          <t>Lamina microcorrugada E K/K/K 45x69</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -5146,7 +5146,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Single face E K/K 44,5x65,5</t>
+          <t>Single face E B/K 57,5x70,3</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -5161,7 +5161,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Recipiente industrial 250gr Belga</t>
+          <t>Single face E B/B 54,5x77</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -5176,7 +5176,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Single face E K/K 100x90</t>
+          <t>Single face C K/K 91X87,5</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -5191,7 +5191,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 64x79.5</t>
+          <t>Single face C K/K 87,5x91,5</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -5206,7 +5206,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Single Face B K/K 49,4x49,4</t>
+          <t>Lamina microcorrugada B K/K/BG 87,5x91</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5221,7 +5221,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Single face E B/K 57,5x70,3</t>
+          <t>Funda caja canasta temporadas</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -5236,7 +5236,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SQUARE PLATE 8x8in</t>
+          <t>Estibas malas y retales de madera</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -5251,7 +5251,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SOUP PLATE 12 ONZ</t>
+          <t>Single face E K/K 100x90</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -5266,7 +5266,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SQUARE PLATE 10x10in</t>
+          <t>Single face E BG/BG 64x79.5</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -5281,7 +5281,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>SQUARE PLATE 6x6in</t>
+          <t>Contenedor tapa plana chicharrón</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -5311,7 +5311,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Single face E K/K 45X50</t>
+          <t>Contenedor armable brosty entero</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -5326,7 +5326,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Single face E K/K 33x70</t>
+          <t>Contenedor armable brosty cuarto de poll</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -5341,7 +5341,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Single face E K/K 45X40</t>
+          <t>Single face E K/K 40x40</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -5356,7 +5356,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Contenedor tapa plana chicharrón</t>
+          <t>Contenedor 750 grs CASA DEL ARROZ</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -5371,7 +5371,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada B K/K/BG 87,5x91</t>
+          <t>Caja pizza vito</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -5386,7 +5386,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Funda caja canasta temporadas</t>
+          <t>RECIPIENTE INDUSTRIAL 500GR PX1 NAVIDAD</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -5401,7 +5401,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Single face E K/K 61,3x75,3</t>
+          <t>Porta Obleas 8,4cm</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -5416,7 +5416,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Single face 15x22</t>
+          <t>Single face C K/K 114x70,5</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -5431,7 +5431,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Caja de pizza pequeña Aire Romero</t>
+          <t>Single face B K/K 99,4x63,4</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -5446,7 +5446,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Caja delivery 36 onz  armable</t>
+          <t>Caja pizza  36x36x5 cm makro</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -5461,7 +5461,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Caja delivery 47 onz Food</t>
+          <t>Caja delivery kraft 36 onz</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -5476,7 +5476,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Single face B K/K 59,5X77,5</t>
+          <t>Single face E K/K 47x73,8</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -5491,7 +5491,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Caja Sandupa 25X17X13</t>
+          <t>Single face E K/K 45X50</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -5506,7 +5506,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Caja bel skin PX1</t>
+          <t>Single face E K/K 45X40</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -5521,7 +5521,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Caja canasta temporadas</t>
+          <t>Single face E K/K 44,5x65,5</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -5536,7 +5536,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Single face B K/K 55.5X116</t>
+          <t>Caja delivery 47 onz Food</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -5551,7 +5551,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Single face B K/K 55X116</t>
+          <t>Caja delivery 36 onz  armable</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -5566,7 +5566,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Single face E K/K 61x59,5</t>
+          <t>Caja de pizza pequeña Aire Romero</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -5581,7 +5581,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Single face E K/K 61,5x71</t>
+          <t>Caja canasta temporadas</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -5596,7 +5596,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Single face E K/K 57,5x62,5</t>
+          <t>Caja bel skin PX1</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -5611,7 +5611,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Single face E K/K 57,5X88</t>
+          <t>Caja Sandupa 25X17X13</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -5626,7 +5626,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Single face B K/K 44,5x77,5</t>
+          <t>Single face E K/K 49,5x52</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -5641,7 +5641,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Single face B K/K 104,5x74,5</t>
+          <t>Single face E K/K 49,5X69,5</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -5656,7 +5656,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Single Face E K/K 67x99,5</t>
+          <t>Single face E K/K 48,3X97,3</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -5671,7 +5671,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Single Face E K/K 67,5x42</t>
+          <t>Single face E K/K 56,3X93,3</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -5686,7 +5686,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Single Face B K/K 85.2x58.5</t>
+          <t>Single face E K/K 54,9x37,5</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5701,7 +5701,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Single face E K/K 56,3X93,3</t>
+          <t>Single face B K/K 64,3x53,5</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -5716,7 +5716,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Caja delivery kraft 36 onz</t>
+          <t>Recipiente industrial 250gr Belga</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -5731,7 +5731,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Caja pizza vito</t>
+          <t>Single face E K/K 51,5x42,5</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -5746,7 +5746,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Single face E K/K 51,5x42,5</t>
+          <t>CONTENEDOR P1 HACIENDA</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -5761,7 +5761,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Single face E K/K 54,9x37,5</t>
+          <t>Single face E K/K 57,5x62,5</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -5776,7 +5776,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Single face B B/K 47,6x53,3</t>
+          <t>Single face E K/K 57,5X88</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -5791,7 +5791,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Single face E K/K 49,5x52</t>
+          <t>CAJA PIZZA 31x32x4,5 Divino</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -5806,7 +5806,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Single face E K/K 48,3X97,3</t>
+          <t>CAJA CANASTA NAVIDAD - GREEN &amp; FRESH</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -5821,7 +5821,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Single face E K/K 47x73,8</t>
+          <t>CAJA ARUM VITAL AZUL NAL</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -5836,7 +5836,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Contenedor 750 grs CASA DEL ARROZ</t>
+          <t>CAJA ARUM VITAL AZUL EXPO</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -5851,7 +5851,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Single face E K/K 49,5X69,5</t>
+          <t>Single Face B K/K 85.2x58.5</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -5866,7 +5866,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Contenedor armable brosty cuarto de poll</t>
+          <t>Single Face B K/K 49,4x49,4</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -5881,7 +5881,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Contenedor armable brosty entero</t>
+          <t>SQUARE PLATE 8x8in</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -5896,7 +5896,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Single face E K/K 63,5x52,5</t>
+          <t>SQUARE PLATE 6x6in</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -5911,7 +5911,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 HACIENDA</t>
+          <t>SQUARE PLATE 10x10in</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -5926,7 +5926,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Single face B K/K 51X74</t>
+          <t>SOUP PLATE 12 ONZ</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -5941,7 +5941,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Single face E K/K 76,3x57,3</t>
+          <t>Single face B K/K 69,5X99,5</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -5956,7 +5956,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Single face C K/K 59,5x99,5</t>
+          <t>Bolsa kraft delivery mediana puppys</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -5971,7 +5971,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Single face C K/K 91X87,5</t>
+          <t>Single face E K/K 63,5x52,5</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -5986,7 +5986,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Single face E K/K 71x43,5</t>
+          <t>Single face E K/K 61x59,5</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -6001,7 +6001,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Bandeja formada N8C</t>
+          <t>Single face E K/K 61,5x71</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -6016,7 +6016,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Aislador bottega</t>
+          <t>Single face E K/K 60X58,4</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -6031,7 +6031,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Aislador Kraft Nativos 5cm</t>
+          <t>Single face E K/K 61,3x75,3</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -6046,7 +6046,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Single face E B/B 54,5x77</t>
+          <t>Bolsa blanca pequeña con manigueta 20+12X25 C/M</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -6061,7 +6061,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Aislador kraft Mistral</t>
+          <t>Bolsa Kraft pequeña C/M  Henry Munera</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -6076,7 +6076,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Aislador legrand</t>
+          <t>Single face E K/K 65x83,5</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -6091,7 +6091,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Aislador la tavola</t>
+          <t>Bolsa Kraft mediana C/M  Henry Munera</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -6106,7 +6106,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Single face B K/K 99,4x63,4</t>
+          <t>Blonda # 29,8</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -6121,7 +6121,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Single face C K/K 114x70,5</t>
+          <t>Single Face E K/K 67,5x42</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -6136,7 +6136,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Single face B K/K 64,3x53,5</t>
+          <t>Single face B K/K 59,5X77,5</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -6151,7 +6151,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Bolsa kraft delivery mediana puppys</t>
+          <t>Single face B K/K 55X116</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -6166,7 +6166,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Single face E K/K 65x83,5</t>
+          <t>Single face B K/K 55.5X116</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -6181,7 +6181,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Single face E K/K 65.7x80.7</t>
+          <t>Single face B K/K 51X74</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -6196,7 +6196,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Single face E K/K 65,5x91</t>
+          <t>Single face E K/K 63x53</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -6211,7 +6211,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Single face E K/K 64.3x75.3</t>
+          <t>Single face E K/K 65.7x80.7</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -6226,7 +6226,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Single face E K/K 63x53</t>
+          <t>Single face E K/K 65,5x91</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -6241,7 +6241,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Bolsa blanca pequeña con manigueta 20+12X25 C/M</t>
+          <t>Single face E K/K 64.3x75.3</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -6256,7 +6256,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Bolsa Kraft mediana C/M  Henry Munera</t>
+          <t>Aislador Kraft Nativos 5cm</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -6271,7 +6271,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Bolsa Kraft pequeña C/M  Henry Munera</t>
+          <t>Single face E K/K 69X74,1</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -6286,7 +6286,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Blonda # 29,8</t>
+          <t>Single face B B/K 47,6x53,3</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -6301,7 +6301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Single face B K/K 69,5X99,5</t>
+          <t>Single face 15x22</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -6316,7 +6316,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CAJA PIZZA 31x32x4,5 Divino</t>
+          <t>Single face B K/K 44,5x77,5</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -6331,7 +6331,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Bandeja empanadas sancho paisa</t>
+          <t>Single Face E K/K 67x99,5</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -6346,7 +6346,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>BLONDA #12 PX0 OBLEAS JL</t>
+          <t>Bandeja formada N8C</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -6361,7 +6361,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Bandeja formada #1 Legrand</t>
+          <t>Single face B K/K 104,5x74,5</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -6376,7 +6376,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Blonda # 17 Px1 Kraft Flauta E</t>
+          <t>Aislador legrand</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -6391,7 +6391,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Single face E K/K 69X74,1</t>
+          <t>BLONDA #12 PX0 OBLEAS JL</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -6406,7 +6406,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Single face E K/K 77x113</t>
+          <t>Aislador la tavola</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -6421,7 +6421,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Single face E K/K 60X58,4</t>
+          <t>Aislador kraft Mistral</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -6436,7 +6436,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Single face E B/B 69,5x49,5</t>
+          <t>Aislador bottega</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -6451,11 +6451,11 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CAJA CANASTA NAVIDAD - GREEN &amp; FRESH</t>
+          <t>Single face B K/K 67.5X116</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Single face B K/K 67.5X116</t>
+          <t>Bandeja formada #1 repuje sigmaplas</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -6481,11 +6481,11 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Bandeja formada #1 repuje sigmaplas</t>
+          <t>BANDEJA ONDAS #1</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2.333333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Recipiente Fruver Oscar penagos</t>
+          <t>SQUARE PLATE 4x4in</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -6511,7 +6511,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Cup drink carrier x 4</t>
+          <t>Single face E K/K 72x52</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -6526,7 +6526,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>HIGH TRAY 250 GRS</t>
+          <t>Single face B K/K 89,3X65,8</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -6541,7 +6541,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>TRAY # 7</t>
+          <t>Recipiente Fruver Oscar penagos</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -6556,7 +6556,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Contenedor C1 TA HACIENDA</t>
+          <t>Plato sopero 8onz (R)</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -6571,7 +6571,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Single face E B/K 76,8X55,8</t>
+          <t>Bandeja plana #25 Pollo Salvaje</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -6586,7 +6586,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Single face E B/K 44,5X34,5</t>
+          <t>Single face E B/K 76,8X55,8</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -6601,7 +6601,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>SQUARE PLATE 4x4in</t>
+          <t>Single face E K/K 33x70</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -6616,7 +6616,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BANDEJA ONDAS #1</t>
+          <t>PARRILLA 13X13,7 B/B ILEGALE</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -6631,7 +6631,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TRAY # 4</t>
+          <t>Cup drink carrier x 2</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -6646,7 +6646,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>TAKE-OUT CONTAINER P1</t>
+          <t>Cup drink carrier x 4</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -6661,7 +6661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>PARRILLA 13X13,7 B/B ILEGALE</t>
+          <t>Cup sleeve</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -6676,7 +6676,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Plato sopero 8onz (R)</t>
+          <t>HIGH TRAY 500 GRS</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -6691,7 +6691,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>TAKE-OUT CONTAINER C1</t>
+          <t>HIGH TRAY 250 GRS</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -6706,7 +6706,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Single face E K/K 72x52</t>
+          <t>Single face C K/K 99,5x69,5</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -6721,7 +6721,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CAJA ARUM LIFE ROSADA NAL</t>
+          <t>Single face E B/K 44,5X34,5</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -6736,7 +6736,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Bandeja plana #25 Pollo Salvaje</t>
+          <t>TRAY # 4</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -6751,7 +6751,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Single face C K/K 99,5x69,5</t>
+          <t>TAKE-OUT CONTAINER 750</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -6766,7 +6766,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Single face B K/K 89,3X65,8</t>
+          <t>TAKE-OUT CONTAINER C1</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -6781,7 +6781,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Cup sleeve</t>
+          <t>TAKE-OUT CONTAINER P1</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -6796,7 +6796,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Cup drink carrier x 2</t>
+          <t>TRAY # 8</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -6811,7 +6811,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>HIGH TRAY 500 GRS</t>
+          <t>Contenedor C1 TA HACIENDA</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -6826,7 +6826,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TAKE-OUT CONTAINER 750</t>
+          <t>CAJA ARUM LIFE ROSADA NAL</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -6841,7 +6841,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>TRAY # 8</t>
+          <t>TRAY # 7</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -6856,7 +6856,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Single face E K/K 50X45</t>
+          <t>Aislador cocorollo</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -6871,7 +6871,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Single face E K/K 90x105</t>
+          <t>Single face E K/K 74,5X101</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -6886,7 +6886,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Aislador cocorollo</t>
+          <t>Single face E K/K 50X45</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -6901,7 +6901,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Single face E K/K 74,5X101</t>
+          <t>Single face E K/K 90x105</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -6916,11 +6916,11 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>VTARTL VENTA PAPEL</t>
+          <t>Caja delivery 64 onz Olive</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>3</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Single face E K/K 78X59,5</t>
+          <t>Bandeja formada #7 repuje sigmaplas</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -6946,7 +6946,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Single face E K/K 58x96.4</t>
+          <t>Single face B K/K 64,3x60,3</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -6961,7 +6961,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Single face E B/K 47,2X86</t>
+          <t>Blonda #40 cm hacienda</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -6976,7 +6976,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>VTACHT CHATARRA</t>
+          <t>Blonda #21 cm hacienda</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -6991,7 +6991,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Single face E B/K 56,2X101,7</t>
+          <t>Blonda # 17 Px1 Kraft Flauta E</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -7006,7 +7006,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada B K/K/K 80x77</t>
+          <t>Parrillas Caja doble Pizza</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -7021,7 +7021,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 105x60</t>
+          <t>Bandeja fruver #4</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -7036,7 +7036,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Single face B K/K 109x74,5</t>
+          <t>Single face C K/K 46,5x86</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -7051,7 +7051,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Single face B K/K 49,5x88</t>
+          <t>Single face E B/K 47,2X86</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -7066,7 +7066,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Single face E K/K 59,5x90,8</t>
+          <t>PORTA SANDUPA</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -7081,7 +7081,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TA ZUANA</t>
+          <t>Blonda #31 cm hacienda</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -7096,7 +7096,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Single face E K/K 55,3X102,8</t>
+          <t>Single face E B/K 56,2X101,7</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -7111,7 +7111,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Contenedor C1 TA Belga</t>
+          <t>Single face E B/B 70x100</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -7126,7 +7126,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Single face E K/K 50x80</t>
+          <t>Single face E B/B 70x50</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -7141,7 +7141,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Caja wok beige 16onz</t>
+          <t>Lamina microcorrugada E K/K/K 105x60</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -7156,7 +7156,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Contenedor arepa sancho paisa</t>
+          <t>Single face E K/K 110x100</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -7171,7 +7171,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP AIRE ROMERO</t>
+          <t>Lamina microcorrugada B K/K/K 80x77</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -7186,7 +7186,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Single face E K/K 50x61</t>
+          <t>PLATO CUADRADO 15x15 PX0 SIN IMPRESION (R)</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -7201,7 +7201,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Contenedor armable brosty medio pollo</t>
+          <t>Single face B K/K 74,3X59,7</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -7216,7 +7216,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Single face E K/K 110x100</t>
+          <t>Recipiente 350g Px2 Granel</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7231,7 +7231,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 79,5x64</t>
+          <t>Caja wok beige 16onz</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7246,7 +7246,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPRESION</t>
+          <t>CAJA NAVIDAD MEDIANA KRAFT - 1 TINTA</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -7261,7 +7261,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Recipiente 350g Px2 Granel</t>
+          <t>Caja regalo Kraft mediana</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -7276,7 +7276,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Caja plegadiza Franco Química</t>
+          <t>Single face B K/K 91X67</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -7291,7 +7291,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Caja regalo Kraft mediana</t>
+          <t>Single face B K/K 69,5X60,5</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -7306,7 +7306,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Single face B B/K 69,2x41,5</t>
+          <t>SERVICIO DE IMPRESION</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -7321,7 +7321,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Caja Bel Skin - 1 Tinta</t>
+          <t>Single face B K/K 78,8X65,3</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -7351,7 +7351,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Single face E K/K 73,5x44</t>
+          <t>Single face B K/K 70x59,5</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -7366,7 +7366,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Single face B K/K 74,3X59,7</t>
+          <t>Single face E K/K 70x82</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -7381,7 +7381,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Single face B K/K 91X67</t>
+          <t>Single face E K/K 73,5x44</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -7396,7 +7396,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Blonda #40 cm hacienda</t>
+          <t>Single face B K/K 49,5x88</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -7411,7 +7411,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Single face B K/K 69,5X60,5</t>
+          <t>Single face B B/K 69,2x41,5</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -7426,7 +7426,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>PLATO CUADRADO 15x15 PX0 SIN IMPRESION (R)</t>
+          <t>Single face B K/K 109x74,5</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -7441,7 +7441,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>PORTA SANDUPA</t>
+          <t>Contenedor P1 TP AIRE ROMERO</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -7456,7 +7456,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Caja Refrigerio Multivasos</t>
+          <t>Contenedor arepa sancho paisa</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -7471,7 +7471,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Caja delivery 36 onz Food</t>
+          <t>Caja plegadiza Franco Química</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -7486,7 +7486,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Caja delivery 47 onz armable</t>
+          <t>Single face E K/K 60,2x60,3</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -7516,7 +7516,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CAJA NAVIDAD MEDIANA KRAFT - 1 TINTA</t>
+          <t>Caja delivery 47 onz armable</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -7531,7 +7531,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Single face E K/K 60,2x60,3</t>
+          <t>Single face E K/K 59,5x90,8</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -7546,7 +7546,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Single face E B/B 70x100</t>
+          <t>Caja Refrigerio Multivasos</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -7561,7 +7561,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Single face B K/K 70x59,5</t>
+          <t>VTARTL VENTA PAPEL</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -7576,7 +7576,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x82</t>
+          <t>Caja Bel Skin - 1 Tinta</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -7591,7 +7591,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Single face C K/K 46,5x86</t>
+          <t>CONTENEDOR P1 TA ZUANA</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -7606,7 +7606,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,5x45,5</t>
+          <t>Single face E K/K 55,3X102,8</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -7621,7 +7621,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Bandeja formada #7 repuje sigmaplas</t>
+          <t>Single face E K/K 58x96.4</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -7636,7 +7636,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Single face B K/K 64,3x60,3</t>
+          <t>Caja delivery 36 onz Food</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -7651,7 +7651,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Single face E B/B 70x50</t>
+          <t>Single face E K/K 50x61</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -7666,7 +7666,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Single face B K/K 78,8X65,3</t>
+          <t>Single face E K/K 50x80</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -7681,7 +7681,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Bandeja fruver #4</t>
+          <t>Contenedor armable brosty medio pollo</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -7696,7 +7696,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Blonda #31 cm hacienda</t>
+          <t>Single face E BG/BG 79,5x64</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -7711,7 +7711,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Blonda #21 cm hacienda</t>
+          <t>Single face E K/K 78X59,5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -7726,11 +7726,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Single face E B/B 41,3x47,3</t>
+          <t>Single face E K/K 89,5x45,5</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -7741,11 +7741,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Single face E K/K 99,9x65,2</t>
+          <t>VTACHT CHATARRA</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -7756,11 +7756,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Single face E K/K 41,3x81,7</t>
+          <t>Single face E K/K 99,9x65,2</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>3.5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -7771,11 +7771,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Caja delivery 64 onz Olive</t>
+          <t>Single face E B/B 41,3x47,3</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>3.5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Contenedor fresas tapa alta</t>
+          <t>Single face B K/K 66X60.5</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -7801,7 +7801,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Caja wok kraft 8onz</t>
+          <t>Single face E K/K 41,3x81,7</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -7816,7 +7816,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Single face B K/K 66X60.5</t>
+          <t>Contenedor C1 TA Belga</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -7831,7 +7831,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Single face B K/K 71x77,3</t>
+          <t>Caja wok kraft 8onz</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -7846,11 +7846,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Parrilla contenedor P1 TP</t>
+          <t>Contenedor fresas tapa alta</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>3.666666666666667</v>
+        <v>3.5</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -7861,11 +7861,11 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Single face E K/K 63.8x76.7</t>
+          <t>Single face B K/K 71x77,3</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>3.666666666666667</v>
+        <v>3.5</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x50</t>
+          <t>Parrilla contenedor P1 TP</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -7906,11 +7906,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>BANDEJA PLANA # 1  NAVIDAD - 1 TINTA</t>
+          <t>Single face E K/K 63.8x76.7</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>4</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -7921,11 +7921,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Single face E B/B 70x33</t>
+          <t>Single face E K/K 70x50</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>4</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Single face B K/K 64,5x108</t>
+          <t>Lamina microcorrugada E K/K/K 48,5x74,5</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -7951,7 +7951,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Single face B K/K 90,5X66,5</t>
+          <t>Plato cuadrado 25x25 (R)</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -7966,7 +7966,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Single face B K/K 111,5x67,5</t>
+          <t>Lamina microcorrugada E K/K/K 60x100</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -7981,7 +7981,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Single face B K/K 57,5x89,5</t>
+          <t>Single face E K/K 69.3x84.3</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -7996,7 +7996,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>RECIPIENTE KRAFT 500 GR IMPRESO</t>
+          <t>Single face E K/K 79,5x64,5</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -8011,7 +8011,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>SERVICIO PEGADO</t>
+          <t>Single face E K/K 55X97</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -8026,7 +8026,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Single face E K/K 35x70</t>
+          <t>Molde pan rectangular 250gr</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -8041,7 +8041,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Plato cuadrado 25x25 (R)</t>
+          <t>Bolsa kraft pequeña con manigueta matena</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -8056,7 +8056,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Capacillo ponque artesano bimbo</t>
+          <t>Single face E K/K 35x70</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -8071,7 +8071,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Single face E K/K 46.3X73.3</t>
+          <t>Contenedor P1 Tapa Plana il Forno</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -8086,7 +8086,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 60x100</t>
+          <t>Capacillo ponque artesano bimbo</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -8101,7 +8101,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 48,5x74,5</t>
+          <t>Caja delivery 36 onz Olive</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -8131,7 +8131,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Molde pan rectangular 250gr</t>
+          <t>Caja delivery kraft 47 onz</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -8146,7 +8146,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Single face E K/K 55X97</t>
+          <t>Single face E K/K 46.3X73.3</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -8161,7 +8161,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Caja delivery kraft 47 onz</t>
+          <t>BANDEJA PLANA # 1  NAVIDAD - 1 TINTA</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -8191,7 +8191,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>BLONDA 21CM</t>
+          <t>Single face E K/K 79x79</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -8206,7 +8206,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CAJA 1 CERVEZA 3 COPAS + PARRILLA</t>
+          <t>BLONDA 21CM</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -8221,7 +8221,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Bolsa kraft pequeña con manigueta matena</t>
+          <t>Bandeja Fruver # 3  Teres</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -8236,7 +8236,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Single face E K/K 79,5x64,5</t>
+          <t>Single face B K/K 64,5x108</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -8251,7 +8251,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Single face E K/K 79x79</t>
+          <t>Single face B K/K 57,5x89,5</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -8266,7 +8266,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Bandeja fruver 13x13 PX0</t>
+          <t>CAJA 1 CERVEZA 3 COPAS + PARRILLA</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -8281,7 +8281,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 3  Teres</t>
+          <t>RECIPIENTE KRAFT 500 GR IMPRESO</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -8296,7 +8296,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Single face E K/K 69.3x84.3</t>
+          <t>SERVICIO PEGADO</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -8311,7 +8311,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Caja delivery 36 onz Olive</t>
+          <t>Bandeja fruver 13x13 PX0</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -8326,11 +8326,11 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Bandeja arepitas con yuca y queso x 14un</t>
+          <t>Single face E B/B 70x33</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
@@ -8341,11 +8341,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TA HOTWINGS-NO USAR</t>
+          <t>Single face B K/K 90,5X66,5</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -8356,11 +8356,11 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Portavasos k/k x 2 unds (R)</t>
+          <t>Single face B K/K 111,5x67,5</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
@@ -8371,11 +8371,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Single face E K/K 49x43</t>
+          <t>CONTENEDOR C1 TA HOTWINGS-NO USAR</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>4.666666666666667</v>
+        <v>4.5</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -8386,11 +8386,11 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Caja BG/K 30x30x10 - Maxi pastel</t>
+          <t>Single face E K/K 49x43</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TP NAVIDAD DRY VENTANA - 4</t>
+          <t>Single face E B/K 70X100</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -8416,7 +8416,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>COMISION POR VENTAS</t>
+          <t>Plato redondo 9in Drop</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -8431,7 +8431,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Bandeja fruver #1</t>
+          <t>Lamina microcorrugada E B/K/K 70x100</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -8446,7 +8446,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP-Kive</t>
+          <t>Portavasos k/k x 2 unds (R)</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -8461,7 +8461,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E K/K/K 65,2x58,6</t>
+          <t>Bandeja fruver #1</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -8476,7 +8476,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E B/K/K 70x100</t>
+          <t>Single face B K/K 61x79,5</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -8491,7 +8491,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Aislador kraft (R)</t>
+          <t>Bandeja arepitas con yuca y queso x 14un</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -8506,7 +8506,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Plato redondo 9in Drop</t>
+          <t>Single Face B K/K 88x70,5</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -8521,7 +8521,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Recipiente industrial 250 gr makro</t>
+          <t>Contenedor P1 TP-Kive</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -8536,7 +8536,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Single face B K/K 61x79,5</t>
+          <t>COMISION POR VENTAS</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -8551,7 +8551,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Single face E K/K 89,5x86,5</t>
+          <t>Lamina microcorrugada E K/K/K 65,2x58,6</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -8566,7 +8566,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Single Face B K/K 88x70,5</t>
+          <t>Caja BG/K 30x30x10 - Maxi pastel</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -8581,7 +8581,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Single face E B/K 70X100</t>
+          <t>CONTENEDOR C1 TP NAVIDAD DRY VENTANA - 4</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -8596,7 +8596,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 7 3.5 alto la calera</t>
+          <t>Single face E K/K 89,5x86,5</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -8611,7 +8611,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Bandeja plana #8 makro</t>
+          <t>Bandeja Fruver # 7 3.5 alto la calera0x0</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -8641,7 +8641,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 7 3.5 alto la calera0x0</t>
+          <t>Recipiente industrial 250 gr makro</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -8656,7 +8656,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>BANDEJA PLANA # 7 NAVIDAD - 1 TINTA</t>
+          <t>Bandeja plana #1 granel</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -8671,7 +8671,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Single face B BG/BG 70x59,5</t>
+          <t>BANDEJA PLANA # 7 NAVIDAD - 1 TINTA</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -8686,7 +8686,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Bandeja plana #1 granel</t>
+          <t>Aislador kraft (R)</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -8701,11 +8701,11 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Single face E K/K 70x100</t>
+          <t>Single face B BG/BG 70x59,5</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>5.666666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -8716,11 +8716,11 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MUESTRAS</t>
+          <t>Single face E K/K 70x100</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>6</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -8731,11 +8731,11 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Caja wok kraft 32onz</t>
+          <t>Bandeja Fruver # 7 3.5 alto la calera</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>6</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Bolsa kraft boutique con manigueta 25,5+13x33</t>
+          <t>CONTENEDOR P1 TA HOTWINGS</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -8761,7 +8761,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CAJA PIZZA ROMERO PEQUEÑA</t>
+          <t>Single face E K/K 47x76,1</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -8776,7 +8776,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Bandeja fruver #8</t>
+          <t>Single face E K/K 55X90.5</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -8791,7 +8791,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Single face E K/K 47x76,1</t>
+          <t>Caja Bel Skin 0X0</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -8806,7 +8806,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 79,5x64,5</t>
+          <t>Caja BG/K 34x34x11 - Maxi pastel</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -8821,7 +8821,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 41x49.5</t>
+          <t>Plato sopero 8onz (D)</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -8836,7 +8836,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Plato sopero 8onz (D)</t>
+          <t>CAJA PIZZA ROMERO PEQUEÑA</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -8851,7 +8851,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Single face E K/K 55X90.5</t>
+          <t>Single face E BG/BG 79,5x64,5</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -8866,7 +8866,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TA HOTWINGS</t>
+          <t>Caja wok kraft 32onz</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -8881,7 +8881,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Caja BG/K 34x34x11 - Maxi pastel</t>
+          <t>Single face E BG/BG 41x49.5</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -8896,7 +8896,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Caja Bel Skin 0X0</t>
+          <t>MUESTRAS</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -8911,52 +8911,52 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Single face B K/K 64x84,5</t>
+          <t>Bandeja fruver #8</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>frecuente</t>
+          <t>esporadico</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TP NAVIDAD - 4 TINTAS</t>
+          <t>Bolsa kraft boutique con manigueta 25,5+13x33</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>frecuente</t>
+          <t>esporadico</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>FUNDA SANGRIA 2 Lt NAVIDAD</t>
+          <t>Bandeja plana #8 makro</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>frecuente</t>
+          <t>esporadico</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP-Kive</t>
+          <t>FUNDA SANGRIA 2 Lt NAVIDAD</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -8971,7 +8971,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TA HOTWINGS</t>
+          <t>Plato sopero 12onz</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -8986,7 +8986,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Plato sopero 12onz</t>
+          <t>Single face B K/K 64x84,5</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -9001,11 +9001,11 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Bandeja formada #1 granel</t>
+          <t>CONTENEDOR C1 TA HOTWINGS</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
@@ -9016,11 +9016,11 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Single face E K/K 57,5x89,5</t>
+          <t>CONTENEDOR C1 TP NAVIDAD - 4 TINTAS</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
@@ -9031,11 +9031,11 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TP NAVIDAD DRY VENTANA - 4</t>
+          <t>Contenedor C1 TP-Kive</t>
         </is>
       </c>
       <c r="B575" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Recipiente industrial 500 gr makro</t>
+          <t>Single face B K/K 59,3X78,3</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -9076,7 +9076,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Recipiente industrial 1000 gr makro</t>
+          <t>Bandeja formada #1 granel</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -9106,7 +9106,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Single face B K/K 59,3X78,3</t>
+          <t>CONTENEDOR P1 TP NAVIDAD DRY VENTANA - 4</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -9151,11 +9151,11 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Separador tacos</t>
+          <t>Recipiente industrial 500 gr makro</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>7.666666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -9166,11 +9166,11 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Plato cuadrado 20x20 (R)</t>
+          <t>Recipiente industrial 1000 gr makro</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -9181,11 +9181,11 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Single face B K/K 55X90,5</t>
+          <t>Single face E K/K 57,5x89,5</t>
         </is>
       </c>
       <c r="B585" t="n">
-        <v>8</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -9196,11 +9196,11 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Plato cuadrado 25x25 (D)</t>
+          <t>Separador tacos</t>
         </is>
       </c>
       <c r="B586" t="n">
-        <v>8</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>NO DEFINIDO</t>
+          <t>Base caja pizza long</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -9226,7 +9226,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Base caja pizza long</t>
+          <t>CONTENEDOR P1 TA HOTWINGS-NO USAR</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -9241,7 +9241,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TA HOTWINGS-NO USAR</t>
+          <t>Plato cuadrado 20x20 (R)</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -9256,11 +9256,11 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Bandeja plana #7 makro</t>
+          <t>CONTENEDOR EXTRAGRANDE</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>8</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CONTENEDOR EXTRAGRANDE</t>
+          <t>Salseros de Papel 4 onz</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -9286,7 +9286,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Single face E K/K 40,2X70,8</t>
+          <t>Single face B K/K 55X90,5</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -9301,7 +9301,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Salseros de Papel 4 onz</t>
+          <t>Single face E K/K 40,2X70,8</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -9316,7 +9316,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TAPA PLANA MAKRO</t>
+          <t>Plato cuadrado 25x25 (D)</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -9346,7 +9346,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TAPA PLANA MAKRO</t>
+          <t>PLATO REDONDO 6`` NAVIDAD - 1 TINTA</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -9361,7 +9361,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Parrilla contenedor 600gr TP</t>
+          <t>Caja delivery 27 onz</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -9376,7 +9376,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>PLATO REDONDO 6`` NAVIDAD - 1 TINTA</t>
+          <t>Bandeja plana #7 makro</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -9391,7 +9391,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>FUNDA SANGRÍA 4 LITROS NAVIDAD</t>
+          <t>Parrilla contenedor 600gr TP</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -9406,7 +9406,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Caja delivery 27 onz</t>
+          <t>CONTENEDOR P1 TAPA PLANA MAKRO</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -9421,11 +9421,11 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Lamina microcorrugada E B/B/B 70x100</t>
+          <t>FUNDA SANGRÍA 4 LITROS NAVIDAD</t>
         </is>
       </c>
       <c r="B601" t="n">
-        <v>9.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blonda # 17 Px0 </t>
+          <t>Lamina microcorrugada E B/B/B 70x100</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -9451,11 +9451,11 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP SPORTWINGS(nuevo)</t>
+          <t>NO DEFINIDO</t>
         </is>
       </c>
       <c r="B603" t="n">
-        <v>9.5</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -9466,11 +9466,11 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>SERVICIO PLASTIFICADO BIOLOUMAX</t>
+          <t>Blonda # 17 Px0</t>
         </is>
       </c>
       <c r="B604" t="n">
-        <v>9.666666666666666</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -9481,11 +9481,11 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Bolsa mediana PCA x 250unds - ARC</t>
+          <t>Contenedor C1 TP SPORTWINGS(nuevo)</t>
         </is>
       </c>
       <c r="B605" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
@@ -9496,11 +9496,11 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Contenedor 600gr TP Carbon 100</t>
+          <t>CONTENEDOR C1 TAPA PLANA MAKRO</t>
         </is>
       </c>
       <c r="B606" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
@@ -9511,11 +9511,11 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Caja delivery kraft 64 onz</t>
+          <t>SERVICIO PLASTIFICADO BIOLOUMAX</t>
         </is>
       </c>
       <c r="B607" t="n">
-        <v>10</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>BLONDA 15,5 PLASTIFICADO POR AMBOS LADOS</t>
+          <t>Caja delivery kraft 64 onz</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -9541,11 +9541,11 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>BOLSA MEDIA PORCIÓN ADICIONALES PAQx100</t>
+          <t>Contenedor 600gr TP Carbon 100</t>
         </is>
       </c>
       <c r="B609" t="n">
-        <v>10.33333333333333</v>
+        <v>10</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
@@ -9556,11 +9556,11 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Bandeja plana #8 granel</t>
+          <t>Bolsa mediana PCA x 250unds - ARC</t>
         </is>
       </c>
       <c r="B610" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
@@ -9571,11 +9571,11 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP starbucks PL</t>
+          <t>BLONDA 15,5 PLASTIFICADO POR AMBOS LADOS</t>
         </is>
       </c>
       <c r="B611" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
@@ -9586,11 +9586,11 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TP NAVIDAD - 4 TINTAS</t>
+          <t>BOLSA MEDIA PORCIÓN ADICIONALES PAQx100</t>
         </is>
       </c>
       <c r="B612" t="n">
-        <v>10.5</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="C612" t="inlineStr">
         <is>
@@ -9601,11 +9601,11 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 3 PX1</t>
+          <t>CONTENEDOR P1 TP NAVIDAD - 4 TINTAS</t>
         </is>
       </c>
       <c r="B613" t="n">
-        <v>10.66666666666667</v>
+        <v>10.5</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
@@ -9616,11 +9616,11 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Caja delivery beige 47 onz</t>
+          <t>Bandeja Fruver # 3 PX1</t>
         </is>
       </c>
       <c r="B614" t="n">
-        <v>11</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Bandeja plana #1 makro</t>
+          <t>Contenedor C1 TP starbucks PL</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -9646,11 +9646,11 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Bolsa grande PCA x 300unds - ARC</t>
+          <t>Caja delivery beige 47 onz</t>
         </is>
       </c>
       <c r="B616" t="n">
-        <v>11.33333333333333</v>
+        <v>11</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
@@ -9661,11 +9661,11 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Bandeja formada #4</t>
+          <t>Bandeja plana #8 granel</t>
         </is>
       </c>
       <c r="B617" t="n">
-        <v>11.33333333333333</v>
+        <v>11</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
@@ -9676,11 +9676,11 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Single face E K/K 51,3x80,3</t>
+          <t>Bolsa grande PCA x 300unds - ARC</t>
         </is>
       </c>
       <c r="B618" t="n">
-        <v>11.66666666666667</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
@@ -9691,11 +9691,11 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Plato cuadrado 15x15 (D)</t>
+          <t>Bandeja formada #4</t>
         </is>
       </c>
       <c r="B619" t="n">
-        <v>11.66666666666667</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Bandeja 18.5x10x2 Sary PX2 IMPRESO</t>
+          <t>Single face E K/K 51,3x80,3</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -9736,7 +9736,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>FUNDA SANGRÍA 1 LITROS NAVIDAD</t>
+          <t>Bandeja plana #1 makro</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -9751,7 +9751,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Caja maletin multipack 1 tinta (ARTE NUE</t>
+          <t>Plato cuadrado 15x15 (D)</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -9766,11 +9766,11 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>RECIPIENTE INDUSTRIAL 500GR PX2</t>
+          <t>FUNDA SANGRÍA 1 LITROS NAVIDAD</t>
         </is>
       </c>
       <c r="B624" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
@@ -9781,11 +9781,11 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Single face B K/K 55,5X90,5</t>
+          <t>Caja maletin multipack 1 tinta (ARTE NUE</t>
         </is>
       </c>
       <c r="B625" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
@@ -9796,11 +9796,11 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>SERVICIO PLASTIFICADO BRILLANTE</t>
+          <t>Bandeja 18.5x10x2 Sary PX2 IMPRESO</t>
         </is>
       </c>
       <c r="B626" t="n">
-        <v>13</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
@@ -9811,11 +9811,11 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Bandeja fruver #17 bolsita</t>
+          <t>RECIPIENTE INDUSTRIAL 500GR PX2</t>
         </is>
       </c>
       <c r="B627" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
@@ -9826,11 +9826,11 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Plato redondo 6 in</t>
+          <t>Single face B K/K 55,5X90,5</t>
         </is>
       </c>
       <c r="B628" t="n">
-        <v>13.66666666666667</v>
+        <v>13</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
@@ -9841,11 +9841,11 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Caja regalo beige grande</t>
+          <t>Bandeja fruver #17 bolsita</t>
         </is>
       </c>
       <c r="B629" t="n">
-        <v>13.66666666666667</v>
+        <v>13.5</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
@@ -9856,11 +9856,11 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Single face B K/K 91X87,5</t>
+          <t>SERVICIO PLASTIFICADO BRILLANTE</t>
         </is>
       </c>
       <c r="B630" t="n">
-        <v>14</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="C630" t="inlineStr">
         <is>
@@ -9871,11 +9871,11 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Single face E K/K 49,5X61</t>
+          <t>Caja regalo beige grande</t>
         </is>
       </c>
       <c r="B631" t="n">
-        <v>14</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="C631" t="inlineStr">
         <is>
@@ -9886,11 +9886,11 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Single face E BG/BG 49.5x52.5</t>
+          <t>Single face E K/K 49,5X61</t>
         </is>
       </c>
       <c r="B632" t="n">
-        <v>14.33333333333333</v>
+        <v>14</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
@@ -9901,11 +9901,11 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>CAJA PIZZA ROMERO GRANDE</t>
+          <t>Single face B K/K 91X87,5</t>
         </is>
       </c>
       <c r="B633" t="n">
-        <v>14.33333333333333</v>
+        <v>14</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
@@ -9916,11 +9916,11 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Blonda # 17 Px1</t>
+          <t>Plato redondo 6 in</t>
         </is>
       </c>
       <c r="B634" t="n">
-        <v>14.33333333333333</v>
+        <v>14</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
@@ -9931,11 +9931,11 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Bandeja formada #7 granel</t>
+          <t>Blonda # 17 Px1</t>
         </is>
       </c>
       <c r="B635" t="n">
-        <v>14.5</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
@@ -9946,11 +9946,11 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Single face E K/K 48x46</t>
+          <t>Single face E BG/BG 49.5x52.5</t>
         </is>
       </c>
       <c r="B636" t="n">
-        <v>14.66666666666667</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
@@ -9961,11 +9961,11 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Plato redondo 10 in</t>
+          <t>Bandeja formada #7 granel</t>
         </is>
       </c>
       <c r="B637" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
@@ -9976,11 +9976,11 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Caja regalo beige mediana</t>
+          <t>Single face E K/K 48x46</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>15</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
@@ -10006,11 +10006,11 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>BLONDA #19 PLASTIFICADA POR AMBOS LADOS</t>
+          <t>Caja regalo beige mediana</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>15.33333333333333</v>
+        <v>15</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
@@ -10021,11 +10021,11 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Bandeja fruver #3 sin plastificar</t>
+          <t>BLONDA #19 PLASTIFICADA POR AMBOS LADOS</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>16</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="C641" t="inlineStr">
         <is>
@@ -10036,11 +10036,11 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Single face E K/K 99,4x63,4</t>
+          <t>Plato redondo 10 in</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>16</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
@@ -10051,11 +10051,11 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>PLATO REDONDO 9`` NAVIDAD - 1 TINTA</t>
+          <t>CAJA PIZZA ROMERO GRANDE</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>16</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="C643" t="inlineStr">
         <is>
@@ -10066,11 +10066,11 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>SERVICIO PLASTIFICADO LECHOSO</t>
+          <t>Single face E K/K 99,4x63,4</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>16.33333333333333</v>
+        <v>16</v>
       </c>
       <c r="C644" t="inlineStr">
         <is>
@@ -10081,11 +10081,11 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Plato cuadrado 20x20 (D)</t>
+          <t>PLATO REDONDO 9`` NAVIDAD - 1 TINTA</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="C645" t="inlineStr">
         <is>
@@ -10096,11 +10096,11 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Bandeja arepita con queso doble cremax10unds(masma</t>
+          <t>SERVICIO PLASTIFICADO LECHOSO</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>16.5</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="C646" t="inlineStr">
         <is>
@@ -10111,11 +10111,11 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>PAPEL DE HORNEO SIN IMPRESIÓN (25X30)</t>
+          <t>Bandeja arepita con queso doble cremax10unds(masma</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>16.66666666666667</v>
+        <v>16.5</v>
       </c>
       <c r="C647" t="inlineStr">
         <is>
@@ -10126,11 +10126,11 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Contenedor C1 TA starbucks PL</t>
+          <t>Plato cuadrado 20x20 (D)</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="C648" t="inlineStr">
         <is>
@@ -10141,11 +10141,11 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Contenedor 600gr TP Carnivoro</t>
+          <t>PAPEL DE HORNEO SIN IMPRESIÓN (25X30)</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>17.33333333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
@@ -10156,11 +10156,11 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Bolsa Kraft Pequeña C/M starbucks</t>
+          <t>Bandeja fruver #3 sin plastificar</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>17.33333333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
@@ -10171,11 +10171,11 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Contenedor 600gr TP Archies</t>
+          <t>Contenedor C1 TA starbucks PL</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>17.66666666666667</v>
+        <v>17</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
@@ -10186,11 +10186,11 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Bolsa kraft mediana C/M starbucks</t>
+          <t>Contenedor 600gr TP Carnivoro</t>
         </is>
       </c>
       <c r="B652" t="n">
-        <v>18</v>
+        <v>17.33333333333333</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
@@ -10201,11 +10201,11 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Plato redondo 9 in</t>
+          <t>Bolsa Kraft Pequeña C/M starbucks</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>18</v>
+        <v>17.33333333333333</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
@@ -10216,11 +10216,11 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>BANDEJA  FORMADA Nº8C GRANEL</t>
+          <t>Contenedor 600gr TP Archies</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>18</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
@@ -10231,11 +10231,11 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Plato sopero 16onz</t>
+          <t>BANDEJA  FORMADA Nº8C GRANEL</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>18.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
@@ -10246,11 +10246,11 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Caja regalo beige pequeña</t>
+          <t>Plato redondo 9 in</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>18.66666666666667</v>
+        <v>18</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
@@ -10261,11 +10261,11 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP Archies</t>
+          <t>Bolsa kraft mediana C/M starbucks</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
@@ -10276,11 +10276,11 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP Archies</t>
+          <t>Plato sopero 16onz</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>19</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
@@ -10291,11 +10291,11 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Bolsa kraft delivery pequeña (20.5+12x25 cms S/M)</t>
+          <t>Caja regalo beige pequeña</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>20</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
@@ -10306,11 +10306,11 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Bandeja plana #7 granel</t>
+          <t>Contenedor C1 TP Archies</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
@@ -10321,11 +10321,11 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Plato cuadrado 10x10</t>
+          <t>Contenedor P1 TP Archies</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>21.33333333333333</v>
+        <v>19</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
@@ -10336,11 +10336,11 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Bandeja plana #25</t>
+          <t>Bolsa kraft delivery pequeña (20.5+12x25 cms S/M)</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>22.66666666666667</v>
+        <v>20</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
@@ -10351,11 +10351,11 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Portavasos k/k x 2 unds Starbucks</t>
+          <t>Bandeja plana #7 granel</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>23.66666666666667</v>
+        <v>21</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
@@ -10366,11 +10366,11 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>PORTA CALIENTE KRAFT 23,5X14,7</t>
+          <t>Plato cuadrado 10x10</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>24</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
@@ -10381,11 +10381,11 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TP SPORTWINGS</t>
+          <t>Bandeja plana #25</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>24.33333333333333</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
@@ -10396,11 +10396,11 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Portavasos k/k x 2 unds Starbucks</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>24.33333333333333</v>
+        <v>24</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>SERVICIO TROQUELADO</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -10426,11 +10426,11 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP Big Boy</t>
+          <t>PORTA CALIENTE KRAFT 23,5X14,7</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>25.66666666666667</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
@@ -10441,11 +10441,11 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>BLONDA 17 PLASTIFICADO POR AMBOS LADOS</t>
+          <t>CONTENEDOR P1 TP SPORTWINGS</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>28.33333333333333</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
@@ -10456,11 +10456,11 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP Big Boy</t>
+          <t>Contenedor C1 TP Big Boy</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>29.66666666666667</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
@@ -10471,11 +10471,11 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Bandeja Fruver # 7 sin plastificar</t>
+          <t>SERVICIO TROQUELADO</t>
         </is>
       </c>
       <c r="B671" t="n">
-        <v>32.33333333333334</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
@@ -10486,11 +10486,11 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP SPORTWINGS</t>
+          <t>BLONDA 17 PLASTIFICADO POR AMBOS LADOS</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>32.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
@@ -10501,11 +10501,11 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Bolsa kraft grande con manigueta (31+17x42.5cms C/M)</t>
+          <t>Contenedor P1 TP Big Boy</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>32.66666666666666</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
@@ -10516,11 +10516,11 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Bandeja fruver #3 Granel</t>
+          <t>Contenedor C1 TP SPORTWINGS</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>33.33333333333334</v>
+        <v>32.5</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
@@ -10531,11 +10531,11 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Plato sopero 8onz</t>
+          <t>Bandeja Fruver # 7 sin plastificar</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>33.5</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
@@ -10546,11 +10546,11 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Bolsa kraft delivery grande(31+17x42.5 cms S/M)</t>
+          <t>Bolsa kraft grande con manigueta (31+17x42.5cms C/M)</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>33.66666666666666</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
@@ -10561,11 +10561,11 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CAJA TORTA RECTANGULAR 25X16</t>
+          <t>Bandeja fruver #3 Granel</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>34.66666666666666</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
@@ -10576,11 +10576,11 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>CAJA TORTA 30X30X10</t>
+          <t>Plato sopero 8onz</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>37</v>
+        <v>33.5</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
@@ -10591,11 +10591,11 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Bandeja fruver #17 granel</t>
+          <t>Bolsa kraft delivery grande(31+17x42.5 cms S/M)</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>38.66666666666666</v>
+        <v>34</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
@@ -10606,11 +10606,11 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Caja torta 26X26X10</t>
+          <t>CAJA TORTA RECTANGULAR 25X16</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
@@ -10621,11 +10621,11 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Bolsa kraft delivery mediana(25+17x35 cms S/M)</t>
+          <t>CAJA TORTA 30X30X10</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
@@ -10636,11 +10636,11 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CAJA TORTA PORCION PERSONAL</t>
+          <t>Bandeja fruver #17 granel</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>42.66666666666666</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
@@ -10651,11 +10651,11 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>CONTENEDOR 1000GR TAPA ALTA</t>
+          <t>Caja torta 26X26X10</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>43.33333333333334</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
@@ -10666,11 +10666,11 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Bolsa kraft mediana con manigueta(25+17x35 cms C/M)</t>
+          <t>Bolsa kraft delivery mediana(25+17x35 cms S/M)</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>43.33333333333334</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
@@ -10681,11 +10681,11 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Bandeja formada #1</t>
+          <t>CAJA TORTA PORCION PERSONAL</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>44.33333333333334</v>
+        <v>43</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
@@ -10696,11 +10696,11 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>CONTENEDOR SUSHI TAPA ALTA</t>
+          <t>CONTENEDOR 1000GR TAPA ALTA</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>45.66666666666666</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
@@ -10711,11 +10711,11 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Contenedor C1 TP EL CORREO</t>
+          <t>Bolsa kraft mediana con manigueta(25+17x35 cms C/M)</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>46</v>
+        <v>43.66666666666666</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
@@ -10726,11 +10726,11 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Plato cuadrado 25x25</t>
+          <t>Bandeja formada #1</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>46</v>
+        <v>44.33333333333334</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
@@ -10741,11 +10741,11 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>CONTENEDOR 600GR TAPA PLANA</t>
+          <t>Plato cuadrado 25x25</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>46.33333333333334</v>
+        <v>46</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
@@ -10756,11 +10756,11 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Bandeja fruver #6</t>
+          <t>CONTENEDOR SUSHI TAPA ALTA</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
@@ -10771,11 +10771,11 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Contenedor P1 TP EL CORREO</t>
+          <t>Contenedor C1 TP EL CORREO</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>50.33333333333334</v>
+        <v>46.33333333333334</v>
       </c>
       <c r="C691" t="inlineStr">
         <is>
@@ -10786,11 +10786,11 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Salseros de Papel 2 onz</t>
+          <t>CONTENEDOR 600GR TAPA PLANA</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>51.66666666666666</v>
+        <v>47.66666666666666</v>
       </c>
       <c r="C692" t="inlineStr">
         <is>
@@ -10801,11 +10801,11 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Bandeja plana #4</t>
+          <t>Contenedor P1 TP EL CORREO</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>57.66666666666666</v>
+        <v>50.66666666666666</v>
       </c>
       <c r="C693" t="inlineStr">
         <is>
@@ -10816,11 +10816,11 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Bandeja formada #7</t>
+          <t>Bandeja fruver #6</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>59.33333333333334</v>
+        <v>51</v>
       </c>
       <c r="C694" t="inlineStr">
         <is>
@@ -10831,11 +10831,11 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Recipiente industrial 350 gr</t>
+          <t>Salseros de Papel 2 onz</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>59.33333333333334</v>
+        <v>52</v>
       </c>
       <c r="C695" t="inlineStr">
         <is>
@@ -10846,11 +10846,11 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Bandeja plana #10</t>
+          <t>Bandeja plana #4</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>59.66666666666666</v>
+        <v>58</v>
       </c>
       <c r="C696" t="inlineStr">
         <is>
@@ -10861,11 +10861,11 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Plato cuadrado 20x20</t>
+          <t>Bandeja formada #7</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>60</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="C697" t="inlineStr">
         <is>
@@ -10876,11 +10876,11 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Bandeja plana #1</t>
+          <t>Plato cuadrado 20x20</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>62.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="C698" t="inlineStr">
         <is>
@@ -10891,11 +10891,11 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Plato cuadrado 15x15</t>
+          <t>Recipiente industrial 350 gr</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>63.5</v>
+        <v>60.33333333333334</v>
       </c>
       <c r="C699" t="inlineStr">
         <is>
@@ -10906,11 +10906,11 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Bolsa kraft pequeña con manigueta (20.5+12x25 cms C/M)</t>
+          <t>Bandeja plana #10</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>63.66666666666666</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="C700" t="inlineStr">
         <is>
@@ -10921,11 +10921,11 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Contenedor C1 tapa alta</t>
+          <t>Plato cuadrado 15x15</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="C701" t="inlineStr">
         <is>
@@ -10936,11 +10936,11 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>CONTENEDOR 750GR TAPA PLANA</t>
+          <t>Bandeja plana #1</t>
         </is>
       </c>
       <c r="B702" t="n">
-        <v>74</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="C702" t="inlineStr">
         <is>
@@ -10951,11 +10951,11 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>CONTENEDOR 1000GR TAPA PLANA</t>
+          <t>Bolsa kraft pequeña con manigueta (20.5+12x25 cms C/M)</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>77.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="C703" t="inlineStr">
         <is>
@@ -10966,11 +10966,11 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>CONTENEDOR P2 TAPA PLANA</t>
+          <t>Contenedor C1 tapa alta</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>78</v>
+        <v>69.33333333333333</v>
       </c>
       <c r="C704" t="inlineStr">
         <is>
@@ -10981,11 +10981,11 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>SERVICIO ENCOLADO</t>
+          <t>CONTENEDOR 750GR TAPA PLANA</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>82.33333333333333</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="C705" t="inlineStr">
         <is>
@@ -10996,11 +10996,11 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>CONTENEDOR P2 TAPA ALTA</t>
+          <t>CONTENEDOR P2 TAPA PLANA</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C706" t="inlineStr">
         <is>
@@ -11011,11 +11011,11 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>SERVICIO CORRUGADO</t>
+          <t>CONTENEDOR 1000GR TAPA PLANA</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>106.6666666666667</v>
+        <v>79</v>
       </c>
       <c r="C707" t="inlineStr">
         <is>
@@ -11026,11 +11026,11 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Salseros de Papel 1 onz</t>
+          <t>SERVICIO ENCOLADO</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>117.3333333333333</v>
+        <v>82.33333333333333</v>
       </c>
       <c r="C708" t="inlineStr">
         <is>
@@ -11041,11 +11041,11 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Recipiente industrial 1000 gr</t>
+          <t>CONTENEDOR P2 TAPA ALTA</t>
         </is>
       </c>
       <c r="B709" t="n">
-        <v>119.3333333333333</v>
+        <v>104.3333333333333</v>
       </c>
       <c r="C709" t="inlineStr">
         <is>
@@ -11056,11 +11056,11 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Portavasos k/k por 4 unds</t>
+          <t>SERVICIO CORRUGADO</t>
         </is>
       </c>
       <c r="B710" t="n">
-        <v>126.6666666666667</v>
+        <v>107.6666666666667</v>
       </c>
       <c r="C710" t="inlineStr">
         <is>
@@ -11071,11 +11071,11 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Bandeja plana #8</t>
+          <t>Recipiente industrial 1000 gr</t>
         </is>
       </c>
       <c r="B711" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C711" t="inlineStr">
         <is>
@@ -11086,11 +11086,11 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Recipiente industrial 250 gr</t>
+          <t>Salseros de Papel 1 onz</t>
         </is>
       </c>
       <c r="B712" t="n">
-        <v>127.3333333333333</v>
+        <v>120.6666666666667</v>
       </c>
       <c r="C712" t="inlineStr">
         <is>
@@ -11101,11 +11101,11 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>CONTENEDOR P1 TAPA ALTA</t>
+          <t>Recipiente industrial 250 gr</t>
         </is>
       </c>
       <c r="B713" t="n">
-        <v>149.3333333333333</v>
+        <v>127.6666666666667</v>
       </c>
       <c r="C713" t="inlineStr">
         <is>
@@ -11116,11 +11116,11 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Recipiente industrial 500 gr</t>
+          <t>Portavasos k/k por 4 unds</t>
         </is>
       </c>
       <c r="B714" t="n">
-        <v>155.6666666666667</v>
+        <v>128.3333333333333</v>
       </c>
       <c r="C714" t="inlineStr">
         <is>
@@ -11131,11 +11131,11 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>CONTENEDOR C1 TAPA PLANA</t>
+          <t>Bandeja plana #8</t>
         </is>
       </c>
       <c r="B715" t="n">
-        <v>203.3333333333333</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="C715" t="inlineStr">
         <is>
@@ -11146,11 +11146,11 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Bandeja plana #7</t>
+          <t>CONTENEDOR P1 TAPA ALTA</t>
         </is>
       </c>
       <c r="B716" t="n">
-        <v>204</v>
+        <v>150.3333333333333</v>
       </c>
       <c r="C716" t="inlineStr">
         <is>
@@ -11161,11 +11161,11 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Aislador kraft</t>
+          <t>Recipiente industrial 500 gr</t>
         </is>
       </c>
       <c r="B717" t="n">
-        <v>215.6666666666667</v>
+        <v>157.6666666666667</v>
       </c>
       <c r="C717" t="inlineStr">
         <is>
@@ -11176,11 +11176,11 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>VTARTL VENTA RETAL</t>
+          <t>CONTENEDOR C1 TAPA PLANA</t>
         </is>
       </c>
       <c r="B718" t="n">
-        <v>244.6666666666667</v>
+        <v>206</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
@@ -11191,11 +11191,11 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Portavasos k/k x 2 unds</t>
+          <t>Bandeja plana #7</t>
         </is>
       </c>
       <c r="B719" t="n">
-        <v>271.3333333333333</v>
+        <v>207</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
@@ -11206,11 +11206,11 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>FLETE FLETE VENTAS</t>
+          <t>Aislador kraft</t>
         </is>
       </c>
       <c r="B720" t="n">
-        <v>272.6666666666667</v>
+        <v>219.6666666666667</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
@@ -11221,11 +11221,11 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Salseros de Papel 0.75 onz</t>
+          <t>VTARTL VENTA RETAL</t>
         </is>
       </c>
       <c r="B721" t="n">
-        <v>272.6666666666667</v>
+        <v>246.6666666666667</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
@@ -11236,13 +11236,58 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
+          <t>Portavasos k/k x 2 unds</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>275</v>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>frecuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Salseros de Papel 0.75 onz</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>275.6666666666667</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>frecuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>FLETE FLETE VENTAS</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>276</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>frecuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
           <t>CONTENEDOR P1 TAPA PLANA</t>
         </is>
       </c>
-      <c r="B722" t="n">
-        <v>326.6666666666667</v>
-      </c>
-      <c r="C722" t="inlineStr">
+      <c r="B725" t="n">
+        <v>329.3333333333333</v>
+      </c>
+      <c r="C725" t="inlineStr">
         <is>
           <t>frecuente</t>
         </is>
